--- a/ExcelFiles/Insert Checkbox.xlsx
+++ b/ExcelFiles/Insert Checkbox.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Excel_Github\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746E69DF-496D-49D8-9D30-7BE208E22AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413A61DB-0202-4703-A2C5-1B978B8CA283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10569" yWindow="1494" windowWidth="14943" windowHeight="11778" activeTab="1" xr2:uid="{EF2CB7EF-1A29-475A-8734-1D679A5585C2}"/>
+    <workbookView xWindow="10569" yWindow="1494" windowWidth="14943" windowHeight="11778" xr2:uid="{EF2CB7EF-1A29-475A-8734-1D679A5585C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Add Checkbox" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>Employee Name</t>
   </si>
@@ -78,12 +78,18 @@
   <si>
     <t>Emp.Name</t>
   </si>
+  <si>
+    <t>True/False</t>
+  </si>
+  <si>
+    <t>N.B- have a hidden column</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,8 +112,25 @@
     </font>
     <font>
       <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -125,13 +148,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <fgColor theme="4" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.499984740745262"/>
+        <fgColor theme="7" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -178,7 +201,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -189,22 +211,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -255,7 +280,7 @@
           <xdr:col>3</xdr:col>
           <xdr:colOff>17253</xdr:colOff>
           <xdr:row>2</xdr:row>
-          <xdr:rowOff>34505</xdr:rowOff>
+          <xdr:rowOff>34506</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
@@ -336,14 +361,19 @@
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
+      <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
           <xdr:colOff>17253</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>34505</xdr:rowOff>
+          <xdr:rowOff>34506</xdr:rowOff>
         </xdr:from>
-        <xdr:ext cx="707366" cy="138023"/>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>724619</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>172528</xdr:rowOff>
+        </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="1055" name="Check Box 31" hidden="1">
@@ -352,7 +382,7 @@
                   <a14:compatExt spid="_x0000_s1055"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E08D8EF-E012-468F-8E77-E91AA564E798}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001F040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -411,20 +441,25 @@
           </xdr:txBody>
         </xdr:sp>
         <xdr:clientData/>
-      </xdr:oneCellAnchor>
+      </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
+      <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
           <xdr:colOff>17253</xdr:colOff>
           <xdr:row>4</xdr:row>
-          <xdr:rowOff>34505</xdr:rowOff>
+          <xdr:rowOff>34506</xdr:rowOff>
         </xdr:from>
-        <xdr:ext cx="707366" cy="138023"/>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>724619</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>172528</xdr:rowOff>
+        </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="1056" name="Check Box 32" hidden="1">
@@ -433,7 +468,7 @@
                   <a14:compatExt spid="_x0000_s1056"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD121EEE-2550-4591-A381-B4190165E6AA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000020040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -492,20 +527,25 @@
           </xdr:txBody>
         </xdr:sp>
         <xdr:clientData/>
-      </xdr:oneCellAnchor>
+      </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
+      <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
           <xdr:colOff>17253</xdr:colOff>
           <xdr:row>5</xdr:row>
-          <xdr:rowOff>34505</xdr:rowOff>
+          <xdr:rowOff>34506</xdr:rowOff>
         </xdr:from>
-        <xdr:ext cx="707366" cy="138023"/>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>724619</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>172528</xdr:rowOff>
+        </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="1057" name="Check Box 33" hidden="1">
@@ -514,7 +554,7 @@
                   <a14:compatExt spid="_x0000_s1057"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55A2B465-29DC-4640-8AFA-C68EB0DF411C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000021040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -573,20 +613,25 @@
           </xdr:txBody>
         </xdr:sp>
         <xdr:clientData/>
-      </xdr:oneCellAnchor>
+      </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:oneCellAnchor>
+      <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>3</xdr:col>
           <xdr:colOff>17253</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>34505</xdr:rowOff>
+          <xdr:rowOff>34506</xdr:rowOff>
         </xdr:from>
-        <xdr:ext cx="707366" cy="138023"/>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>724619</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>172528</xdr:rowOff>
+        </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="1058" name="Check Box 34" hidden="1">
@@ -595,7 +640,7 @@
                   <a14:compatExt spid="_x0000_s1058"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00B1ECC3-A2BF-4339-9E04-3F53062B370E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000022040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -654,7 +699,7 @@
           </xdr:txBody>
         </xdr:sp>
         <xdr:clientData/>
-      </xdr:oneCellAnchor>
+      </xdr:twoCellAnchor>
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
@@ -681,7 +726,7 @@
                   <a14:compatExt spid="_x0000_s1059"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4C5A5EB-3212-7699-6999-FA6EF432B298}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000023040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1064,12 +1109,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26F0CD0F-E867-474F-A47E-F0494FE9E659}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="15.375" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.25" customWidth="1"/>
+    <col min="5" max="5" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1082,101 +1128,133 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <v>17558962458</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9" t="b">
+      <c r="D3" s="8"/>
+      <c r="E3" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="8" t="str">
+        <f>IF(E3,  "Yes", "No")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <v>1585974563</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9" t="b">
+      <c r="D4" s="8"/>
+      <c r="E4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="8" t="str">
+        <f t="shared" ref="F4:F8" si="0">IF(E4,  "Yes", "No")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9" t="b">
+      <c r="C5" s="7"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>30360001227</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9" t="b">
+      <c r="D6" s="8"/>
+      <c r="E6" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>46332989122</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9" t="b">
+      <c r="D7" s="8"/>
+      <c r="E7" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9" t="b">
+      <c r="C8" s="7"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B11:F11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -1331,62 +1409,62 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="14"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C4" s="17" t="str">
+      <c r="C4" s="13" t="str">
         <f>'Add Checkbox'!B3</f>
         <v>Jahid</v>
       </c>
-      <c r="D4" s="18" t="b">
-        <f>'Add Checkbox'!E3</f>
-        <v>1</v>
+      <c r="D4" s="14" t="str">
+        <f>IF('Add Checkbox'!E3, "Yes", "No")</f>
+        <v>Yes</v>
       </c>
     </row>
     <row r="5" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C5" s="17" t="str">
+      <c r="C5" s="13" t="str">
         <f>'Add Checkbox'!B4</f>
         <v>Jobayer</v>
       </c>
-      <c r="D5" s="18" t="b">
-        <f>'Add Checkbox'!E4</f>
-        <v>1</v>
+      <c r="D5" s="14" t="str">
+        <f>IF('Add Checkbox'!E4, "Yes", "No")</f>
+        <v>Yes</v>
       </c>
     </row>
     <row r="6" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C6" s="17" t="str">
+      <c r="C6" s="13" t="str">
         <f>'Add Checkbox'!B5</f>
         <v>jakir</v>
       </c>
-      <c r="D6" s="18" t="b">
-        <f>'Add Checkbox'!E5</f>
-        <v>0</v>
+      <c r="D6" s="14" t="str">
+        <f>IF('Add Checkbox'!E5, "Yes", "No")</f>
+        <v>No</v>
       </c>
     </row>
     <row r="7" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C7" s="17" t="str">
+      <c r="C7" s="13" t="str">
         <f>'Add Checkbox'!B6</f>
         <v>fahim</v>
       </c>
-      <c r="D7" s="18" t="b">
-        <f>'Add Checkbox'!E6</f>
-        <v>1</v>
+      <c r="D7" s="14" t="str">
+        <f>IF('Add Checkbox'!E6, "Yes", "No")</f>
+        <v>Yes</v>
       </c>
     </row>
     <row r="8" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C8" s="17" t="str">
+      <c r="C8" s="13" t="str">
         <f>'Add Checkbox'!B7</f>
         <v>juel</v>
       </c>
-      <c r="D8" s="18" t="b">
-        <f>'Add Checkbox'!E7</f>
-        <v>1</v>
+      <c r="D8" s="14" t="str">
+        <f>IF('Add Checkbox'!E7, "Yes", "No")</f>
+        <v>Yes</v>
       </c>
     </row>
   </sheetData>
